--- a/public/exports/29189501.xlsx
+++ b/public/exports/29189501.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M120"/>
+  <dimension ref="A1:O120"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -24,55 +24,65 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ejerskab</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Primær registreret ejer</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Geografisk kommunekode</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t xml:space="preserve">Adresse</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Postnr.</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Energimærkningsfirma</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -91,53 +101,63 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Agnetevej 40</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">9740</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">749167, 3189683</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H2">
+      <c r="J2">
         <v>441</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -156,53 +176,63 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Anemonevej 5</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">9320</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">749192, 3188800</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>2020</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -221,53 +251,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Anemonevej 7</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">9320</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">3189134</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>669</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -286,53 +326,63 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Anlægsvej 23</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">9740</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">749163, 3204607</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H5">
+      <c r="J5">
         <v>394</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -351,53 +401,63 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Døvlingvej 12</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve">749160, 5508712</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H6">
+      <c r="J6">
         <v>257</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -416,53 +476,63 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Døvlingvej 8</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve">5508711</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>279</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,53 +551,63 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Fredensgade 3</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">9330</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t xml:space="preserve">3187063</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>275</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -546,53 +626,63 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Golfvejen 63</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve">9039635</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H9">
+      <c r="J9">
         <v>430</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -611,53 +701,63 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Golfvejen 83</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t xml:space="preserve">749165, 5505439</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H10">
+      <c r="J10">
         <v>817</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -676,53 +776,63 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Hybenvej 34B</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t xml:space="preserve">749183, 3207731</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="H11">
+      <c r="J11">
         <v>484</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -741,53 +851,63 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Jens Thise Vej 27</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t xml:space="preserve">3212041</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>299</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -806,53 +926,63 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Jens Thise Vej 31</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t xml:space="preserve">749158, 3212041</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="H13">
+      <c r="J13">
         <v>314</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -871,53 +1001,63 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Møllehusvej 7</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">9340</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t xml:space="preserve">749193, 3183190</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H14">
+      <c r="J14">
         <v>2205</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -936,53 +1076,63 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nordens Alle 56</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t xml:space="preserve">5505134</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>993</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1001,53 +1151,63 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nordens Alle 7</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t xml:space="preserve">5505117</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="H16">
+      <c r="J16">
         <v>269</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1066,53 +1226,63 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Rusen 8</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">9340</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t xml:space="preserve">749186, 3183192</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H17">
+      <c r="J17">
         <v>276</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1131,53 +1301,63 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Sdr Ringgade 83</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">9740</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t xml:space="preserve">749266, 3204868</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H18">
+      <c r="J18">
         <v>1062</v>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1196,53 +1376,63 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Skolegade 28</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t xml:space="preserve">9018850</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="H19">
+      <c r="J19">
         <v>2260</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1261,53 +1451,63 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Smørblomstvej 5A</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">9320</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t xml:space="preserve">3189134</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H20">
+      <c r="J20">
         <v>1480</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1326,53 +1526,63 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Smørblomstvej 5A</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">9320</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t xml:space="preserve">3189134</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="H21">
+      <c r="J21">
         <v>260</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1391,53 +1601,63 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Smørblomstvej 5B</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">9320</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t xml:space="preserve">3189134</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="H22">
+      <c r="J22">
         <v>609</v>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1456,53 +1676,63 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Østermarken 120</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">9320</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t xml:space="preserve">100307265</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="H23">
+      <c r="J23">
         <v>649</v>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1521,53 +1751,63 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tømmerbyvej 6</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t xml:space="preserve">9702880</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H24">
+      <c r="J24">
         <v>308</v>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t xml:space="preserve">200027593</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Just A/S</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-02-03</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1586,53 +1826,63 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Hellevadvej 6</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">9320</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t xml:space="preserve">749242, 100020861</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H25">
+      <c r="J25">
         <v>359</v>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t xml:space="preserve">200031183</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">JPH Energi A/S</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-05-06</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1651,53 +1901,63 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Bredgade 60</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t xml:space="preserve">5507855</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H26">
+      <c r="J26">
         <v>938</v>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t xml:space="preserve">311163557</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Just A/S</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-10</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1716,53 +1976,63 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nordens Alle 1</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t xml:space="preserve">5505117</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H27">
+      <c r="J27">
         <v>1621</v>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t xml:space="preserve">311225622</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1781,53 +2051,63 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Lærkevej 40</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t xml:space="preserve">3212342</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H28">
+      <c r="J28">
         <v>634</v>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t xml:space="preserve">311281609</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-10-09</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1846,53 +2126,63 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Klintevej 8</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">9320</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t xml:space="preserve">3189061</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H29">
+      <c r="J29">
         <v>510</v>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t xml:space="preserve">311281369</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-10-31</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1911,53 +2201,63 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Smørblomstvej 5A</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">9320</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t xml:space="preserve">3189134</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H30">
+      <c r="J30">
         <v>1722</v>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t xml:space="preserve">311281362</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-10-31</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1976,53 +2276,63 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Smørblomstvej 5A</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">9320</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t xml:space="preserve">3189134</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H31">
+      <c r="J31">
         <v>528</v>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t xml:space="preserve">311281364</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-10-31</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2041,53 +2351,63 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Baunevej 2</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">9740</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t xml:space="preserve">3205041</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H32">
+      <c r="J32">
         <v>481</v>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t xml:space="preserve">311281634</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-11-01</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2106,53 +2426,63 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Borgergade 30</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">9740</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t xml:space="preserve">3204584</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H33">
+      <c r="J33">
         <v>719</v>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t xml:space="preserve">311281596</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-11-01</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2171,53 +2501,63 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Jens Thise Vej 26</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t xml:space="preserve">3211830</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="H34">
+      <c r="J34">
         <v>315</v>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t xml:space="preserve">311285617</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-11-02</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2236,53 +2576,63 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Jens Thise Vej 26</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t xml:space="preserve">3211830</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H35">
+      <c r="J35">
         <v>843</v>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t xml:space="preserve">311282023</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-11-03</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2301,53 +2651,63 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Jens Thise Vej 26</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t xml:space="preserve">3211830</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="H36">
+      <c r="J36">
         <v>995</v>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t xml:space="preserve">311282023</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-11-03</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2366,53 +2726,63 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Direkte ejer</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t xml:space="preserve">849</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t xml:space="preserve">Redningsvejen Nord 138A</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">9480</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t xml:space="preserve">3228873</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H37">
+      <c r="J37">
         <v>270</v>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t xml:space="preserve">311282015</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-11-03</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2431,53 +2801,63 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">Samsøgade 21</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">9740</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t xml:space="preserve">100002867</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H38">
+      <c r="J38">
         <v>300</v>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t xml:space="preserve">311282014</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-11-03</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2496,53 +2876,63 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Voldgade 67</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">9740</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t xml:space="preserve">3204724</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H39">
+      <c r="J39">
         <v>2617</v>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t xml:space="preserve">311282096</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-11-03</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2561,53 +2951,63 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t xml:space="preserve">Sdr Ringgade 79</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t xml:space="preserve">9740</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t xml:space="preserve">3204868</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H40">
+      <c r="J40">
         <v>5730</v>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t xml:space="preserve">311282230</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-11-05</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2626,53 +3026,63 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t xml:space="preserve">Sdr Ringgade 81</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t xml:space="preserve">9740</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t xml:space="preserve">3204868</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H41">
+      <c r="J41">
         <v>1439</v>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t xml:space="preserve">311282229</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-11-05</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2691,53 +3101,63 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t xml:space="preserve">Elmevej 89</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t xml:space="preserve">3220255</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H42">
+      <c r="J42">
         <v>1775</v>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t xml:space="preserve">311283319</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-11-10</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2756,53 +3176,63 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t xml:space="preserve">Elmevej 104</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t xml:space="preserve">3220645</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H43">
+      <c r="J43">
         <v>311</v>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t xml:space="preserve">311283440</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-11-12</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2821,53 +3251,63 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t xml:space="preserve">Valdemarsgade 25</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t xml:space="preserve">9899097</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H44">
+      <c r="J44">
         <v>2743</v>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t xml:space="preserve">311285917</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-11-27</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2886,53 +3326,63 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t xml:space="preserve">Vestmanna Alle 8</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t xml:space="preserve">5505133</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H45">
+      <c r="J45">
         <v>2707</v>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t xml:space="preserve">311298328</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-11-27</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2951,53 +3401,63 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nordens Alle 33</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t xml:space="preserve">5505150</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H46">
+      <c r="J46">
         <v>1134</v>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t xml:space="preserve">311286305</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-11-29</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3016,53 +3476,63 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t xml:space="preserve">Torvegade 5</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t xml:space="preserve">5507900</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H47">
+      <c r="J47">
         <v>850</v>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t xml:space="preserve">311286928</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-03</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3081,53 +3551,63 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nordens Alle 65</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t xml:space="preserve">8159199</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H48">
+      <c r="J48">
         <v>1459</v>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t xml:space="preserve">311287258</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-05</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3146,53 +3626,63 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t xml:space="preserve">P N Jensens Plads 5</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t xml:space="preserve">5506290</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H49">
+      <c r="J49">
         <v>1630</v>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t xml:space="preserve">311287212</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-05</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3211,53 +3701,63 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t xml:space="preserve">P N Jensens Plads 5</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t xml:space="preserve">5506290</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H50">
+      <c r="J50">
         <v>1078</v>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t xml:space="preserve">311287212</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-05</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3276,53 +3776,63 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t xml:space="preserve">Søndergade 25</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t xml:space="preserve">5509435</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H51">
+      <c r="J51">
         <v>481</v>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t xml:space="preserve">311288317</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3341,53 +3851,63 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t xml:space="preserve">Søndergade 25</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t xml:space="preserve">5509435</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="H52">
+      <c r="J52">
         <v>491</v>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t xml:space="preserve">311288317</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3406,53 +3926,63 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t xml:space="preserve">Fasanvej 10</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t xml:space="preserve">5508685</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H53">
+      <c r="J53">
         <v>513</v>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t xml:space="preserve">311288526</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-13</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3471,53 +4001,63 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t xml:space="preserve">Granvej 13</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t xml:space="preserve">9320</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t xml:space="preserve">10105203</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H54">
+      <c r="J54">
         <v>559</v>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t xml:space="preserve">311289996</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3536,53 +4076,63 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t xml:space="preserve">Hegely 142</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t xml:space="preserve">9320</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t xml:space="preserve">3199887</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H55">
+      <c r="J55">
         <v>461</v>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t xml:space="preserve">311289995</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3601,53 +4151,63 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t xml:space="preserve">Idræts Alle 4</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t xml:space="preserve">9320</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t xml:space="preserve">7250457</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="H56">
+      <c r="J56">
         <v>465</v>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t xml:space="preserve">311289989</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3666,53 +4226,63 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t xml:space="preserve">Idræts Alle 6</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t xml:space="preserve">9320</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t xml:space="preserve">7250457</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H57">
+      <c r="J57">
         <v>3100</v>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t xml:space="preserve">311289987</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3731,53 +4301,63 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t xml:space="preserve">Idræts Alle 6</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t xml:space="preserve">9320</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t xml:space="preserve">7250457</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="H58">
+      <c r="J58">
         <v>1354</v>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t xml:space="preserve">311289988</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3796,53 +4376,63 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t xml:space="preserve">Idræts Alle 6</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t xml:space="preserve">9320</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t xml:space="preserve">7250457</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="H59">
+      <c r="J59">
         <v>696</v>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t xml:space="preserve">311289991</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3861,53 +4451,63 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t xml:space="preserve">Idræts Alle 6</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t xml:space="preserve">9320</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t xml:space="preserve">7250457</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="H60">
+      <c r="J60">
         <v>1223</v>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311289992</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311289993</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3926,53 +4526,63 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t xml:space="preserve">Præstevænget 1</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t xml:space="preserve">9320</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t xml:space="preserve">7250457</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H61">
+      <c r="J61">
         <v>822</v>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t xml:space="preserve">311289983</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3991,53 +4601,63 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t xml:space="preserve">Præstevænget 1B</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t xml:space="preserve">9320</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t xml:space="preserve">7250457</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H62">
+      <c r="J62">
         <v>772</v>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t xml:space="preserve">311289985</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4056,53 +4676,63 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nørre Alle 3A</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t xml:space="preserve">9320</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t xml:space="preserve">407136, 407137</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H63">
+      <c r="J63">
         <v>1628</v>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t xml:space="preserve">311290220</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4121,53 +4751,63 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nordens Alle 56</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t xml:space="preserve">5505134</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H64">
+      <c r="J64">
         <v>6318</v>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t xml:space="preserve">311291398</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-05</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4186,53 +4826,63 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nordens Alle 56</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t xml:space="preserve">5505134</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H65">
+      <c r="J65">
         <v>1956</v>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t xml:space="preserve">311291398</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-05</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4251,53 +4901,63 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nordens Alle 56</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t xml:space="preserve">5505134</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H66">
+      <c r="J66">
         <v>969</v>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t xml:space="preserve">311291398</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-05</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4316,53 +4976,63 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nordens Alle 56</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t xml:space="preserve">5505134</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="H67">
+      <c r="J67">
         <v>523</v>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t xml:space="preserve">311291395</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-05</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4381,53 +5051,63 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ny Rådhusplads 1</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t xml:space="preserve">5505814</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H68">
+      <c r="J68">
         <v>5169</v>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t xml:space="preserve">311291327</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-05</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4446,53 +5126,63 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t xml:space="preserve">Søndergade 40</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t xml:space="preserve">5508607</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H69">
+      <c r="J69">
         <v>2786</v>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t xml:space="preserve">311291376</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-05</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4511,53 +5201,63 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t xml:space="preserve">Søndergade 40</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t xml:space="preserve">5508607</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H70">
+      <c r="J70">
         <v>1052</v>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t xml:space="preserve">311291376</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-05</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
+      <c r="N70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4576,53 +5276,63 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t xml:space="preserve">Søndergade 40</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t xml:space="preserve">5508607</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H71">
+      <c r="J71">
         <v>1851</v>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t xml:space="preserve">311291376</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-05</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4641,53 +5351,63 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t xml:space="preserve">Søndergade 40</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t xml:space="preserve">5508607</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="H72">
+      <c r="J72">
         <v>442</v>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t xml:space="preserve">311291378</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-05</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
+      <c r="N72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4706,53 +5426,63 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nørregade 45</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t xml:space="preserve">9039647</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H73">
+      <c r="J73">
         <v>433</v>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t xml:space="preserve">311292357</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-12</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
+      <c r="N73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4771,53 +5501,63 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t xml:space="preserve">Rømersvej 3</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t xml:space="preserve">5506294</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H74">
+      <c r="J74">
         <v>431</v>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t xml:space="preserve">311293760</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
+      <c r="N74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4836,53 +5576,63 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t xml:space="preserve">Smalbyvej 46</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t xml:space="preserve">5506294</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H75">
+      <c r="J75">
         <v>318</v>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t xml:space="preserve">311293751</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
+      <c r="N75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4901,53 +5651,63 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t xml:space="preserve">Parkvej 55</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t xml:space="preserve">5505023</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H76">
+      <c r="J76">
         <v>732</v>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t xml:space="preserve">311294184</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-24</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
+      <c r="N76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4966,53 +5726,63 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t xml:space="preserve">Fasanvej 20</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t xml:space="preserve">5508658</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H77">
+      <c r="J77">
         <v>582</v>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t xml:space="preserve">311294458</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-25</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
+      <c r="N77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5031,53 +5801,63 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gravensgade 10</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t xml:space="preserve">5505793</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H78">
+      <c r="J78">
         <v>548</v>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t xml:space="preserve">311294714</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-26</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
+      <c r="N78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5096,53 +5876,63 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ingeborg Skeels Vej 31</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t xml:space="preserve">9330</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t xml:space="preserve">3195998</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H79">
+      <c r="J79">
         <v>705</v>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t xml:space="preserve">311294941</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-29</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
+      <c r="N79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5161,53 +5951,63 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ingeborg Skeels Vej 44</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t xml:space="preserve">9330</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t xml:space="preserve">7250213</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H80">
+      <c r="J80">
         <v>460</v>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311294947</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311294950</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-29</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
+      <c r="N80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5226,53 +6026,63 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ingeborg Skeels Vej 44</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t xml:space="preserve">9330</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t xml:space="preserve">7250213</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H81">
+      <c r="J81">
         <v>525</v>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311294947</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311294952</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-29</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
+      <c r="N81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5291,53 +6101,63 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ingeborg Skeels Vej 44</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t xml:space="preserve">9330</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t xml:space="preserve">7250213</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="H82">
+      <c r="J82">
         <v>847</v>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311294947</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311294953</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-29</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
+      <c r="N82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5356,53 +6176,63 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t xml:space="preserve">Margrethelund 4</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t xml:space="preserve">9330</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t xml:space="preserve">100033460</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H83">
+      <c r="J83">
         <v>644</v>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t xml:space="preserve">311294939</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-29</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
+      <c r="N83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5421,53 +6251,63 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t xml:space="preserve">Rørholtvej 20</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t xml:space="preserve">9330</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t xml:space="preserve">8556246</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H84">
+      <c r="J84">
         <v>12136</v>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t xml:space="preserve">311294957</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-29</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
+      <c r="N84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5486,53 +6326,63 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t xml:space="preserve">Rørholtvej 22A</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t xml:space="preserve">9330</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t xml:space="preserve">8556246</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="H85">
+      <c r="J85">
         <v>399</v>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t xml:space="preserve">311294959</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-29</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
+      <c r="N85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5551,53 +6401,63 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t xml:space="preserve">Rusen 5</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t xml:space="preserve">9340</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t xml:space="preserve">3183165</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H86">
+      <c r="J86">
         <v>432</v>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t xml:space="preserve">311295122</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-30</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
+      <c r="N86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5616,53 +6476,63 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t xml:space="preserve">Margrethelund 6</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t xml:space="preserve">9330</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t xml:space="preserve">3186857</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H87">
+      <c r="J87">
         <v>5673</v>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t xml:space="preserve">311295463</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-31</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
+      <c r="N87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5681,53 +6551,63 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t xml:space="preserve">Grønnegade 16</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t xml:space="preserve">5506164</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H88">
+      <c r="J88">
         <v>1021</v>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="K88" t="inlineStr">
         <is>
           <t xml:space="preserve">311295686</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-01</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
+      <c r="N88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5746,53 +6626,63 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t xml:space="preserve">Hedelundsgade 2</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t xml:space="preserve">5505980</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H89">
+      <c r="J89">
         <v>319</v>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t xml:space="preserve">311295952</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-02</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
+      <c r="N89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5811,53 +6701,63 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t xml:space="preserve">Passagen 4</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t xml:space="preserve">5507535</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H90">
+      <c r="J90">
         <v>362</v>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t xml:space="preserve">311295862</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-02</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
+      <c r="N90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5876,53 +6776,63 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mejerigade 9</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t xml:space="preserve">5506223</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H91">
+      <c r="J91">
         <v>562</v>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t xml:space="preserve">311296190</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-05</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
+      <c r="N91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5941,53 +6851,63 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t xml:space="preserve">Skolegade 28</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t xml:space="preserve">9018850</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H92">
+      <c r="J92">
         <v>1289</v>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t xml:space="preserve">311296810</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-08</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
+      <c r="N92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6006,53 +6926,63 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t xml:space="preserve">Skolegade 36</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t xml:space="preserve">9018850</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H93">
+      <c r="J93">
         <v>920</v>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t xml:space="preserve">311296810</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-08</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
+      <c r="N93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6071,53 +7001,63 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t xml:space="preserve">Skolegade 36</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t xml:space="preserve">9018850</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="H94">
+      <c r="J94">
         <v>884</v>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="K94" t="inlineStr">
         <is>
           <t xml:space="preserve">311296810</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-08</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
+      <c r="N94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6136,53 +7076,63 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t xml:space="preserve">Skolegade 36</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t xml:space="preserve">9018850</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="H95">
+      <c r="J95">
         <v>563</v>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="K95" t="inlineStr">
         <is>
           <t xml:space="preserve">311296810</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-08</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
+      <c r="N95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6201,53 +7151,63 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
           <t xml:space="preserve">Elmevej 100</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t xml:space="preserve">3220260</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H96">
+      <c r="J96">
         <v>1670</v>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="K96" t="inlineStr">
         <is>
           <t xml:space="preserve">311298617</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-20</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
+      <c r="N96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6266,53 +7226,63 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
           <t xml:space="preserve">Elmevej 100</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t xml:space="preserve">3220260</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H97">
+      <c r="J97">
         <v>366</v>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="K97" t="inlineStr">
         <is>
           <t xml:space="preserve">311298617</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
+      <c r="L97" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-20</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
+      <c r="N97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6331,53 +7301,63 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
           <t xml:space="preserve">Elmevej 100</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t xml:space="preserve">3220260</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="H98">
+      <c r="J98">
         <v>319</v>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="K98" t="inlineStr">
         <is>
           <t xml:space="preserve">311298614</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-20</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
+      <c r="N98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6396,53 +7376,63 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
           <t xml:space="preserve">Elmevej 122</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t xml:space="preserve">749157, 3220260</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="H99">
+      <c r="J99">
         <v>423</v>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="K99" t="inlineStr">
         <is>
           <t xml:space="preserve">311298617</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-20</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
+      <c r="N99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6461,53 +7451,63 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t xml:space="preserve">Elmevej 122</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t xml:space="preserve">749171, 3220260</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="H100">
+      <c r="J100">
         <v>1929</v>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="K100" t="inlineStr">
         <is>
           <t xml:space="preserve">311298617</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-20</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
+      <c r="N100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6526,53 +7526,63 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
           <t xml:space="preserve">Elmevej 124</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t xml:space="preserve">749259, 3220260</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="H101">
+      <c r="J101">
         <v>555</v>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="K101" t="inlineStr">
         <is>
           <t xml:space="preserve">311298617</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-20</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
+      <c r="N101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6591,53 +7601,63 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
           <t xml:space="preserve">Elmevej 96</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="H102" t="inlineStr">
         <is>
           <t xml:space="preserve">3220260</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="H102">
+      <c r="J102">
         <v>330</v>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="K102" t="inlineStr">
         <is>
           <t xml:space="preserve">311298617</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
+      <c r="L102" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-20</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
+      <c r="N102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6656,53 +7676,63 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
           <t xml:space="preserve">Elmevej 96</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="H103" t="inlineStr">
         <is>
           <t xml:space="preserve">3220260</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H103">
+      <c r="J103">
         <v>738</v>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="K103" t="inlineStr">
         <is>
           <t xml:space="preserve">311298617</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t xml:space="preserve">Energihuset A/S</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-20</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr">
+      <c r="N103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6721,53 +7751,63 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ankervej 1</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t xml:space="preserve">9340</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="H104" t="inlineStr">
         <is>
           <t xml:space="preserve">3182807</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H104">
+      <c r="J104">
         <v>1934</v>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="K104" t="inlineStr">
         <is>
           <t xml:space="preserve">311299953</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-27</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
+      <c r="N104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6786,53 +7826,63 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ankervej 1</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t xml:space="preserve">9340</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="H105" t="inlineStr">
         <is>
           <t xml:space="preserve">3182807</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="H105">
+      <c r="J105">
         <v>966</v>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="K105" t="inlineStr">
         <is>
           <t xml:space="preserve">311299950</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr">
+      <c r="L105" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-27</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
+      <c r="N105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6851,53 +7901,63 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ankervej 1</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t xml:space="preserve">9340</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="H106" t="inlineStr">
         <is>
           <t xml:space="preserve">3182807</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="H106">
+      <c r="J106">
         <v>290</v>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="K106" t="inlineStr">
         <is>
           <t xml:space="preserve">311299946</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
+      <c r="L106" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-27</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
+      <c r="N106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6916,53 +7976,63 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
           <t xml:space="preserve">Dronninglundvej 8</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t xml:space="preserve">9330</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="H107" t="inlineStr">
         <is>
           <t xml:space="preserve">3194680</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H107">
+      <c r="J107">
         <v>413</v>
       </c>
-      <c r="I107" t="inlineStr">
+      <c r="K107" t="inlineStr">
         <is>
           <t xml:space="preserve">311299926</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
+      <c r="L107" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-27</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M107" t="inlineStr">
+      <c r="N107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6981,53 +8051,63 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
           <t xml:space="preserve">Falkevej 1A</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t xml:space="preserve">9330</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="H108" t="inlineStr">
         <is>
           <t xml:space="preserve">3187103</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="I108" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H108">
+      <c r="J108">
         <v>802</v>
       </c>
-      <c r="I108" t="inlineStr">
+      <c r="K108" t="inlineStr">
         <is>
           <t xml:space="preserve">311299899</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr">
+      <c r="L108" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-27</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr">
+      <c r="N108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7046,53 +8126,63 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
           <t xml:space="preserve">Fredensgade 4B</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t xml:space="preserve">9330</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="H109" t="inlineStr">
         <is>
           <t xml:space="preserve">3187092</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="I109" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H109">
+      <c r="J109">
         <v>780</v>
       </c>
-      <c r="I109" t="inlineStr">
+      <c r="K109" t="inlineStr">
         <is>
           <t xml:space="preserve">311299897</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
+      <c r="L109" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-27</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr">
+      <c r="N109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7111,53 +8201,63 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
           <t xml:space="preserve">Multebærvej 5</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t xml:space="preserve">9330</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="H110" t="inlineStr">
         <is>
           <t xml:space="preserve">3187463</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="I110" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H110">
+      <c r="J110">
         <v>1691</v>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="K110" t="inlineStr">
         <is>
           <t xml:space="preserve">311299916</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
+      <c r="L110" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-27</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr">
+      <c r="N110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7176,53 +8276,63 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ankervej 1</t>
+          <t xml:space="preserve">Brønderslev Kommune</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">9340</t>
+          <t xml:space="preserve">810</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">3182807</t>
+          <t xml:space="preserve">Rådhusgade 5</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
+          <t xml:space="preserve">9330</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8646572</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H111">
-        <v>700</v>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311306167</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
+      <c r="J111">
+        <v>804</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311299905</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-04-03</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="M111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-02-27</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7241,53 +8351,63 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ankervej 1</t>
+          <t xml:space="preserve">Brønderslev Kommune</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">9340</t>
+          <t xml:space="preserve">810</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">3182807</t>
+          <t xml:space="preserve">Rådhusgade 5</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
+          <t xml:space="preserve">9330</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8646572</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H112">
-        <v>1081</v>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311306167</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
+      <c r="J112">
+        <v>359</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311299908</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
         <is>
           <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-04-03</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="M112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-02-27</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7306,53 +8426,63 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
           <t xml:space="preserve">Rådhusgade 5</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="G113" t="inlineStr">
         <is>
           <t xml:space="preserve">9330</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="H113" t="inlineStr">
         <is>
           <t xml:space="preserve">8646572</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H113">
-        <v>804</v>
-      </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306035</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="J113">
+        <v>1680</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-03</t>
+          <t xml:space="preserve">311299910</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-02-27</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7371,53 +8501,63 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusgade 5</t>
+          <t xml:space="preserve">Brønderslev Kommune</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slotsgade 47</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
           <t xml:space="preserve">9330</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="H114" t="inlineStr">
         <is>
           <t xml:space="preserve">8646572</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="H114">
-        <v>359</v>
-      </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306035</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="J114">
+        <v>686</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311299913</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2028-04-03</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="M114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2028-02-27</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7436,53 +8576,63 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusgade 5</t>
+          <t xml:space="preserve">Brønderslev Kommune</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">9330</t>
+          <t xml:space="preserve">810</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">8646572</t>
+          <t xml:space="preserve">Ankervej 1</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="H115">
-        <v>1680</v>
+          <t xml:space="preserve">9340</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3182807</t>
+        </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306035</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J115">
+        <v>700</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
+          <t xml:space="preserve">311306167</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-03</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr">
+      <c r="N115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7501,53 +8651,63 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slotsgade 47</t>
+          <t xml:space="preserve">Brønderslev Kommune</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">9330</t>
+          <t xml:space="preserve">810</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">8646572</t>
+          <t xml:space="preserve">Ankervej 1</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
-        </is>
-      </c>
-      <c r="H116">
-        <v>686</v>
+          <t xml:space="preserve">9340</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3182807</t>
+        </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306035</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J116">
+        <v>1081</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
+          <t xml:space="preserve">311306167</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-03</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr">
+      <c r="N116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7566,53 +8726,63 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
           <t xml:space="preserve">Algade 35</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t xml:space="preserve">9320</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="H117" t="inlineStr">
         <is>
           <t xml:space="preserve">8556600</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="I117" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H117">
+      <c r="J117">
         <v>534</v>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="K117" t="inlineStr">
         <is>
           <t xml:space="preserve">311572427</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr">
+      <c r="L117" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-01-14</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr">
+      <c r="N117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7631,53 +8801,63 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
           <t xml:space="preserve">Præstevænget 6B</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="G118" t="inlineStr">
         <is>
           <t xml:space="preserve">9320</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="H118" t="inlineStr">
         <is>
           <t xml:space="preserve">749196, 8556600</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="I118" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H118">
+      <c r="J118">
         <v>304</v>
       </c>
-      <c r="I118" t="inlineStr">
+      <c r="K118" t="inlineStr">
         <is>
           <t xml:space="preserve">311572427</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr">
+      <c r="L118" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-01-14</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
+      <c r="N118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7696,53 +8876,63 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
           <t xml:space="preserve">Bredgade 55</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="G119" t="inlineStr">
         <is>
           <t xml:space="preserve">9700</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="H119" t="inlineStr">
         <is>
           <t xml:space="preserve">412821, 412822</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="I119" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H119">
+      <c r="J119">
         <v>1067</v>
       </c>
-      <c r="I119" t="inlineStr">
+      <c r="K119" t="inlineStr">
         <is>
           <t xml:space="preserve">311728785</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr">
+      <c r="L119" t="inlineStr">
         <is>
           <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-12-13</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
+      <c r="N119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7761,59 +8951,69 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">810</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brønderslev Kommune</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
           <t xml:space="preserve">Hjallerup Erhvervspark 2</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="G120" t="inlineStr">
         <is>
           <t xml:space="preserve">9320</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="H120" t="inlineStr">
         <is>
           <t xml:space="preserve">100017984</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="I120" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H120">
+      <c r="J120">
         <v>755</v>
       </c>
-      <c r="I120" t="inlineStr">
+      <c r="K120" t="inlineStr">
         <is>
           <t xml:space="preserve">311803881</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr">
+      <c r="L120" t="inlineStr">
         <is>
           <t xml:space="preserve">JPH Energi A/S</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-12-20</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="M120" t="inlineStr">
+      <c r="N120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M120"/>
+  <autoFilter ref="A1:O120"/>
 </worksheet>
 </file>
--- a/public/exports/29189501.xlsx
+++ b/public/exports/29189501.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -8314,12 +8314,12 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299905</t>
+          <t xml:space="preserve">311299913</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299908</t>
+          <t xml:space="preserve">311299913</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299910</t>
+          <t xml:space="preserve">311299913</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOE A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M113" t="inlineStr">

--- a/public/exports/29189501.xlsx
+++ b/public/exports/29189501.xlsx
@@ -8314,12 +8314,12 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299913</t>
+          <t xml:space="preserve">311299905</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299913</t>
+          <t xml:space="preserve">311299908</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299913</t>
+          <t xml:space="preserve">311299910</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">MOE A/S</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
